--- a/output/topology_excel/2052.xlsx
+++ b/output/topology_excel/2052.xlsx
@@ -425,58 +425,38 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J3"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>房间1</t>
+          <t>RoomA</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>类型1</t>
+          <t>RoomB</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>面积1</t>
+          <t>ConnectionType</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>房间2</t>
+          <t>Count</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>类型2</t>
+          <t>Length</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>面积2</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>连接类型</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>数量</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>length</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>width</t>
+          <t>Width</t>
         </is>
       </c>
     </row>
@@ -484,37 +464,21 @@
       <c r="A2" t="n">
         <v>1</v>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Living Room</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>259048</v>
+      <c r="B2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
       </c>
       <c r="D2" t="n">
-        <v>2</v>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="E2" t="n">
+        <v>63</v>
       </c>
       <c r="F2" t="n">
-        <v>36203</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>门</t>
-        </is>
-      </c>
-      <c r="H2" t="n">
-        <v>1</v>
-      </c>
-      <c r="I2" t="n">
-        <v>63</v>
-      </c>
-      <c r="J2" t="n">
         <v>13</v>
       </c>
     </row>
@@ -522,37 +486,21 @@
       <c r="A3" t="n">
         <v>1</v>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Living Room</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>259048</v>
+      <c r="B3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
       </c>
       <c r="D3" t="n">
-        <v>2</v>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="E3" t="n">
+        <v>239</v>
       </c>
       <c r="F3" t="n">
-        <v>36203</v>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>墙</t>
-        </is>
-      </c>
-      <c r="H3" t="n">
-        <v>1</v>
-      </c>
-      <c r="I3" t="n">
-        <v>239</v>
-      </c>
-      <c r="J3" t="n">
         <v>208</v>
       </c>
     </row>

--- a/output/topology_excel/2052.xlsx
+++ b/output/topology_excel/2052.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -462,10 +462,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -498,10 +498,142 @@
         <v>1</v>
       </c>
       <c r="E3" t="n">
-        <v>239</v>
+        <v>204</v>
       </c>
       <c r="F3" t="n">
-        <v>208</v>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" t="n">
+        <v>4</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" t="n">
+        <v>226</v>
+      </c>
+      <c r="F4" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" t="n">
+        <v>4</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" t="n">
+        <v>153</v>
+      </c>
+      <c r="F5" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" t="n">
+        <v>3</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" t="n">
+        <v>112</v>
+      </c>
+      <c r="F6" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" t="n">
+        <v>4</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" t="n">
+        <v>79</v>
+      </c>
+      <c r="F7" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>1</v>
+      </c>
+      <c r="B8" t="n">
+        <v>2</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" t="n">
+        <v>75</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>2</v>
+      </c>
+      <c r="B9" t="n">
+        <v>3</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" t="n">
+        <v>170</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/output/topology_excel/2052.xlsx
+++ b/output/topology_excel/2052.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,22 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Length</t>
+          <t>Length_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Width</t>
+          <t>Width_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Length_2</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Width_2</t>
         </is>
       </c>
     </row>
@@ -481,6 +491,8 @@
       <c r="F2" t="n">
         <v>13</v>
       </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -495,14 +507,20 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E3" t="n">
-        <v>204</v>
+        <v>56</v>
       </c>
       <c r="F3" t="n">
         <v>13</v>
       </c>
+      <c r="G3" t="n">
+        <v>73</v>
+      </c>
+      <c r="H3" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -523,8 +541,10 @@
         <v>226</v>
       </c>
       <c r="F4" t="n">
-        <v>44</v>
-      </c>
+        <v>35</v>
+      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -547,6 +567,8 @@
       <c r="F5" t="n">
         <v>13</v>
       </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -569,6 +591,8 @@
       <c r="F6" t="n">
         <v>25</v>
       </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -583,13 +607,19 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E7" t="n">
-        <v>79</v>
+        <v>29</v>
       </c>
       <c r="F7" t="n">
-        <v>42</v>
+        <v>13</v>
+      </c>
+      <c r="G7" t="n">
+        <v>66</v>
+      </c>
+      <c r="H7" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="8">
@@ -613,6 +643,8 @@
       <c r="F8" t="n">
         <v>1</v>
       </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -635,6 +667,8 @@
       <c r="F9" t="n">
         <v>1</v>
       </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
